--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2585-4439-CM25</t>
+          <t>2366-4082-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29816.28</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079596-376-CM25</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4440.47</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1075963-60757-SE25</t>
+          <t>2366-4257-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-14-LR23</t>
+          <t>2239-11-LR24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,47 +676,43 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12754.57</v>
+        <v>1268.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1075963-3750-SE26</t>
+          <t>2585-4244-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-14-LR23</t>
+          <t>2239-11-LR24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -741,62 +737,58 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12754.57</v>
+        <v>3172.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1075963-3757-SE26</t>
+          <t>2369-93-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-14-LR23</t>
+          <t>2239-11-LR24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,17 +798,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -825,13 +817,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12754.57</v>
+        <v>424116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>542429-19-CM26</t>
+          <t>2585-4439-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -841,12 +833,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -856,12 +848,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -886,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7890.56</v>
+        <v>29816.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4022-302-CM26</t>
+          <t>1079596-376-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -902,27 +894,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -932,12 +924,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -947,43 +939,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16382.49</v>
+        <v>4440.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2366-421-CM26</t>
+          <t>1075963-60757-SE25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -993,82 +985,399 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>19992</v>
+        <v>12754.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>1075963-3750-SE26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-14-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>12754.57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1075963-3757-SE26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-14-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SUPER SOFTWARE SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>12754.57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>542429-19-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.979.490-7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>7890.56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4022-302-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.250.800-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Putre</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>16382.49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2366-421-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.854.651-7</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>19992</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2021-131-CM26</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2239-11-LR24</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>61.101.040-0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Estado Mayor Conjunto</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Arica y Parinacota</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Intercity S.A.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>21044.51</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1318,67 +1318,6 @@
       </c>
       <c r="M14" s="2" t="n">
         <v>19992</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2021-131-CM26</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>61.101.040-0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Estado Mayor Conjunto</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Intercity S.A.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>96.826.830-9</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>21044.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,27 +514,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2366-4082-CM25</t>
+          <t>2369-7-SE25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -554,28 +554,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>ORION 2000 SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>96.899.890-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>46532.33</v>
+        <v>413352.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1347870-167-CM25</t>
+          <t>2366-4082-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +589,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -623,20 +627,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29606.49</v>
+        <v>46532.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2366-4257-CM25</t>
+          <t>1347870-167-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +654,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -684,20 +692,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1268.85</v>
+        <v>29606.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2585-4244-CM25</t>
+          <t>2366-4257-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +724,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -745,20 +757,24 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3172.12</v>
+        <v>1268.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2369-93-CM25</t>
+          <t>2585-4244-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,12 +789,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -798,12 +814,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -817,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>424116</v>
+        <v>3172.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2585-4439-CM25</t>
+          <t>2369-93-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,17 +849,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -863,28 +879,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>77.553.790-6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>29816.28</v>
+        <v>424116</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1079596-376-CM25</t>
+          <t>2585-4439-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +914,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -909,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -932,50 +952,54 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>4440.47</v>
+        <v>29816.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1075963-60757-SE25</t>
+          <t>1079596-376-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-14-LR23</t>
+          <t>2239-11-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +1009,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1004,13 +1028,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12754.57</v>
+        <v>4440.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1075963-3750-SE26</t>
+          <t>1075963-60757-SE25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1020,17 +1044,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1075,7 +1099,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1075963-3757-SE26</t>
+          <t>1075963-3750-SE26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1140,22 +1164,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>542429-19-CM26</t>
+          <t>1075963-3757-SE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-11-LR24</t>
+          <t>2239-14-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1165,12 +1189,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1180,28 +1204,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>76.486.150-7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7890.56</v>
+        <v>12754.57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4022-302-CM26</t>
+          <t>542429-19-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1211,27 +1239,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1241,82 +1269,151 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16382.49</v>
+        <v>7890.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>4022-302-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.250.800-9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TECNOLOGIA BS SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.852.815-2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>16382.49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2366-421-CM26</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2239-11-LR24</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>69.010.100-9</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Arica y Parinacota</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>76.854.651-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>19992</v>
       </c>
     </row>
